--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_378_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_378_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="M2" t="n">
         <v>16</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.20</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="M3" t="n">
         <v>4</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1733,10 +1733,10 @@
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1923,7 +1923,7 @@
         <v>4</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         <v>19</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
         <v>1</v>
@@ -2710,13 +2710,13 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="X24" t="n">
         <v>12</v>
@@ -2903,7 +2903,7 @@
         <v>13</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3102,7 +3102,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V26" t="n">
         <v>0</v>
@@ -3298,13 +3298,13 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
         <v>7</v>
@@ -3827,16 +3827,16 @@
         <v>104</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="X30" t="n">
         <v>29</v>
@@ -4292,16 +4292,16 @@
         <v>20</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>4</v>
@@ -4684,7 +4684,7 @@
         <v>9</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -4886,10 +4886,10 @@
         <v>0</v>
       </c>
       <c r="V38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="W38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X38" t="n">
         <v>1</v>
@@ -5076,16 +5076,16 @@
         <v>13</v>
       </c>
       <c r="T39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U39" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V39" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X39" t="n">
         <v>3</v>
@@ -5272,16 +5272,16 @@
         <v>8</v>
       </c>
       <c r="T40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>3</v>
@@ -5471,13 +5471,13 @@
         <v>0</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X41" t="n">
         <v>3</v>
@@ -5664,7 +5664,7 @@
         <v>3</v>
       </c>
       <c r="T42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6062,10 +6062,10 @@
         <v>0</v>
       </c>
       <c r="V44" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X44" t="n">
         <v>2</v>
@@ -6252,16 +6252,16 @@
         <v>5</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X45" t="n">
         <v>1</v>
@@ -6784,16 +6784,16 @@
         <v>115</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="X48" t="n">
         <v>27</v>

--- a/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_378_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/raw/boxscore_full_analysis_378_EL.xlsx
@@ -674,10 +674,10 @@
         <v>16</v>
       </c>
       <c r="N2" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="O2" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="P2" t="n">
         <v>7</v>
@@ -692,20 +692,20 @@
         <v>3</v>
       </c>
       <c r="T2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="V2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>87.88</t>
+          <t>69.23</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>80.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>32.00</t>
+          <t>30.43</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>4</v>
       </c>
       <c r="N3" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="O3" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="P3" t="n">
         <v>6</v>
@@ -864,7 +864,7 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>79.41</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1935,14 +1935,14 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA20" t="n">
@@ -2327,58 +2327,58 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>0.0%</t>
+        </is>
+      </c>
+      <c r="AG22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
           <t>100.0%</t>
         </is>
       </c>
-      <c r="AA22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB22" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AD22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
-      <c r="AG22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>0.0%</t>
-        </is>
-      </c>
       <c r="AJ22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
@@ -2719,14 +2719,14 @@
         <v>7</v>
       </c>
       <c r="X24" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="Y24" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>85.7%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="AA24" t="n">
@@ -2755,7 +2755,7 @@
         <v>0</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
@@ -2766,7 +2766,7 @@
         <v>0</v>
       </c>
       <c r="AK24" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AL24" t="inlineStr">
         <is>
@@ -2915,10 +2915,10 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y25" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
@@ -3307,10 +3307,10 @@
         <v>3</v>
       </c>
       <c r="X27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Y27" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
@@ -3839,14 +3839,14 @@
         <v>12</v>
       </c>
       <c r="X30" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="Y30" t="n">
-        <v>33</v>
+        <v>13</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>87.9%</t>
+          <t>69.2%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3872,25 +3872,25 @@
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AK30" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>30.4%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4304,10 +4304,10 @@
         <v>1</v>
       </c>
       <c r="X35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y35" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -4500,14 +4500,14 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA36" t="n">
@@ -4696,10 +4696,10 @@
         <v>0</v>
       </c>
       <c r="X37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y37" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Y40" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,10 +5480,10 @@
         <v>2</v>
       </c>
       <c r="X41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y41" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
@@ -5872,14 +5872,14 @@
         <v>0</v>
       </c>
       <c r="X43" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Y43" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA43" t="n">
@@ -6796,14 +6796,14 @@
         <v>9</v>
       </c>
       <c r="X48" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="Y48" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="AA48" t="n">
